--- a/AAII_Financials/Yearly/NCNO_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/NCNO_YR_FIN.xlsx
@@ -2752,7 +2752,7 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>220300</v>
+        <v>234600</v>
       </c>
       <c r="E59" s="3">
         <v>191200</v>
